--- a/outputs/E_sideways_invoice.xlsx
+++ b/outputs/E_sideways_invoice.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -36,7 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -86,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -101,6 +105,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -655,6 +662,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -1326,7 +1406,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1.525</v>
+        <v>2.547</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
@@ -1368,7 +1448,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>5.886</v>
+        <v>7.267</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -1410,7 +1490,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5.583</v>
+        <v>7.882</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
@@ -1452,7 +1532,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.923</v>
+        <v>5.488</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1494,7 +1574,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.847</v>
+        <v>1.983</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1536,7 +1616,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.235</v>
+        <v>1.733</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1578,7 +1658,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.287</v>
+        <v>1.248</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1620,7 +1700,7 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3.358</v>
+        <v>7.591</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1651,6 +1731,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1825,7 +2002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1869,7 +2046,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>22.012</v>
+        <v>37.243</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -1998,13 +2175,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2197,8 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2088,6 +2267,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -2135,6 +2324,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -2182,6 +2381,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -2229,6 +2438,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -2276,6 +2495,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -2323,6 +2552,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -2374,6 +2613,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -2425,6 +2674,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -2476,6 +2735,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -2527,6 +2796,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -2578,6 +2857,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -2629,6 +2918,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -2680,6 +2979,16 @@
           <t>comparison</t>
         </is>
       </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -2731,6 +3040,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -2782,6 +3101,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -2833,6 +3162,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -2884,6 +3223,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2935,6 +3284,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2986,6 +3345,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -3037,6 +3406,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -3088,6 +3467,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -3139,6 +3528,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
@@ -3186,6 +3585,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -3233,6 +3642,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
@@ -3280,6 +3699,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -3327,6 +3756,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
@@ -3374,6 +3813,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -3421,23 +3870,33 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M28"/>
+  <autoFilter ref="A1:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -3473,7 +3932,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>5ba0a88daf54b04342255150de98000f4ffc5913a4031026bd7d0ca9789a7dc5</t>
+          <t>340786a4807cc812b4c6f75fc1f6dcbc6176daf566c2fb83ab046afbc3ee3046</t>
         </is>
       </c>
     </row>
@@ -3512,37 +3971,39 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>30</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -3552,30 +4013,80 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B17" s="5" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3640,77 +4151,4 @@
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/E_sideways_invoice.xlsx
+++ b/outputs/E_sideways_invoice.xlsx
@@ -22,15 +22,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$Q$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$X$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -737,59 +737,65 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Time UTC</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Table</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Before</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>After</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Previous hash</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Event hash</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1309,7 +1315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1318,12 +1324,17 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1359,30 +1370,55 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Candidate ID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Selection reason</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Selected</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tables</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Cells</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
@@ -1406,29 +1442,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2.547</v>
+        <v>2.588</v>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
           <t>deskew-300dpi</t>
         </is>
       </c>
-      <c r="G2" s="5" t="b">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>p001-c01</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>ocr-independent-primary</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5" t="n">
+      <c r="M2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="K2" s="5" t="n">
+      <c r="O2" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="P2" s="5" t="n">
         <v>-159.2</v>
       </c>
-      <c r="L2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -1448,29 +1503,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>7.267</v>
+        <v>10.996</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
           <t>cell-recheck-300dpi</t>
         </is>
       </c>
-      <c r="G3" s="5" t="b">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>p001-c02</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>ocr-conditional-recovery</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5" t="n">
+      <c r="M3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="O3" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="P3" s="5" t="n">
         <v>-102.2</v>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -1490,29 +1564,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7.882</v>
+        <v>9.077</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>perspective-cell-recheck-300dpi</t>
         </is>
       </c>
-      <c r="G4" s="5" t="b">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>p001-c03</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>ocr-conditional-recovery</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="n">
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="O4" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="K4" s="5" t="n">
+      <c r="P4" s="5" t="n">
         <v>-102.2</v>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -1532,29 +1625,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5.488</v>
+        <v>7.465</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>second-engine</t>
         </is>
       </c>
-      <c r="G5" s="5" t="b">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>p001-c04</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>ocr-conditional-recovery</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="K5" s="5" t="n">
+      <c r="O5" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="P5" s="5" t="n">
         <v>-139.166</v>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -1574,29 +1686,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.983</v>
+        <v>2.152</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>rotate-90</t>
         </is>
       </c>
-      <c r="G6" s="5" t="b">
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>p001-c05</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>ocr-rotation-recovery</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="M6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="O6" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="P6" s="5" t="n">
         <v>-108.1</v>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="5" t="n">
@@ -1616,29 +1747,48 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.733</v>
+        <v>2.803</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>rotate-180</t>
         </is>
       </c>
-      <c r="G7" s="5" t="b">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>p001-c06</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>ocr-rotation-recovery</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5" t="n">
+      <c r="M7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="J7" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="K7" s="5" t="n">
+      <c r="O7" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="P7" s="5" t="n">
         <v>-134.7</v>
       </c>
-      <c r="L7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -1658,31 +1808,50 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.248</v>
+        <v>2.613</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>rotate-270</t>
         </is>
       </c>
-      <c r="G8" s="5" t="b">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>p001-c07</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>ocr-rotation-recovery</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr"/>
+      <c r="L8" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="M8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="O8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="K8" s="5" t="n">
+      <c r="P8" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="51" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>1</v>
       </c>
@@ -1700,32 +1869,55 @@
         <v>0.999950851003329</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>7.591</v>
+        <v>7.495</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>rotate-270-second-engine</t>
         </is>
       </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>p001-c08</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>ocr-rotation-recovery</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>sequential</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Highest deterministic candidate key: trusted layout, credible content, structural quality, then validation-adjusted score; plan order breaks exact ties.</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="P9" s="5" t="n">
         <v>98.999</v>
       </c>
-      <c r="L9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L9"/>
+  <autoFilter ref="A1:Q9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2046,7 +2238,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>37.243</v>
+        <v>47.411</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -2153,7 +2345,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Ctrl+click a linked data cell for its source bounding box and original readings.</t>
+          <t>Ctrl+click a linked data cell for its source box, confidence meaning, original readings, alternatives and correction count.</t>
         </is>
       </c>
     </row>
@@ -2181,1708 +2373,2823 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="65" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="64" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="65" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="33" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Evidence ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Data sheet</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Excel row</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Working value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Original extracted value</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Original source reading</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Source page</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>x0</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>y0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>x1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>y1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>OCR score</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence type</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Recognition score</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Confidence meaning</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Reading</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Initial reading</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence state</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Location status</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Location reason</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Corrections</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Alternative readings</t>
         </is>
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
+          <t>T1:H:C1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>60.24</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="J2" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="K2" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="L2" s="5" t="n">
         <v>665.04</v>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="n">
         <v>0.9999694426854452</v>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Record</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr"/>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr"/>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="V2" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="5" t="inlineStr"/>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>T1:H:C2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="n">
         <v>60.24</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="J3" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="K3" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="n">
         <v>0.9999520778656006</v>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5" t="inlineStr"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>T1:H:C3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="n">
         <v>60.24</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="J4" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="K4" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="L4" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="n">
         <v>0.9999685287475586</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="V4" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>T1:H:C4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>60.24</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="n">
         <v>0.9906314611434937</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>Unit price</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="V5" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>T1:H:C5</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>60.24</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="J6" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="K6" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="L6" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="n">
         <v>0.9999503095944723</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>header</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>extracted</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
+          <t>T1:R1:C1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="C7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="J7" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="K7" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="L7" s="5" t="n">
         <v>665.04</v>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="n">
         <v>0.9999573628107706</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>T1:R1:C2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Paper</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="K8" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="L8" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="n">
         <v>0.9999287605285645</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Paper</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="S8" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>T1:R1:C3</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="C9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="D9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="K9" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="L9" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="n">
         <v>0.9999651908874512</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t>T1:R1:C4</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="D10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="n">
         <v>0.9999306917190551</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="S10" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>T1:R1:C5</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="C11" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="D11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>24.00</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="n">
         <v>86.88</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="J11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="K11" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="L11" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="n">
         <v>0.999964427947998</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>24.00</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C1</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="K12" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="L12" s="5" t="n">
         <v>665.04</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="n">
         <v>0.9999392032623291</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>A02</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="S12" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="V12" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="inlineStr">
+        <is>
+          <t>comparison: Ad2 (ocr-tesseract)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="K13" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="L13" s="5" t="n">
         <v>665.04</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>ocr-tesseract</t>
         </is>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>Ad2</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Ad2</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>comparison</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
+          <t>comparison: Ad2 (ocr-tesseract)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="C14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="D14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Pens</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Pens</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Pens</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="J14" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="K14" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="n">
         <v>0.9998729228973389</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>Pens</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Pens</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="S14" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="K15" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="L15" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="n">
         <v>0.9999516010284424</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C4</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="D16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="K16" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="L16" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="n">
         <v>0.9999513924121857</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="S16" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>T1:R2:C5</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="D17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="K17" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="L17" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n">
         <v>0.971919572353363</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="V17" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5" t="inlineStr"/>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
+          <t>T1:R3:C1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="K18" s="5" t="n">
         <v>167.76</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="L18" s="5" t="n">
         <v>665.04</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n">
         <v>0.9998644590377808</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>A03</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="S18" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="V18" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
+          <t>T1:R3:C2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Folders</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>167.76</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>605.28</v>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
         <v>0.9998920645032611</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>Folders</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Folders</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="5" t="inlineStr"/>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>T1:R3:C3</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="C20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="D20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="K20" s="5" t="n">
         <v>167.76</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="L20" s="5" t="n">
         <v>414.96</v>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
         <v>0.9999531507492065</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="V20" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>T1:R3:C4</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="J21" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="K21" s="5" t="n">
         <v>167.76</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="L21" s="5" t="n">
         <v>345.12</v>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="n">
         <v>0.9999665319919586</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>7.00</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="V21" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="5" t="inlineStr"/>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
+          <t>T1:R3:C5</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="C22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="D22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="n">
         <v>140.88</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="J22" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="K22" s="5" t="n">
         <v>167.76</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="L22" s="5" t="n">
         <v>255.12</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="n">
         <v>0.9999302148818969</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>28.00</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>28.00</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="5" t="inlineStr"/>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
+          <t>T1:R4:C2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="C23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="D23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Sub Total</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Sub Total</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Sub Total</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="n">
         <v>181.575</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="J23" s="5" t="n">
         <v>560.537</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="K23" s="5" t="n">
         <v>192.018</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="L23" s="5" t="n">
         <v>600.888</v>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="n">
         <v>0.9994450079070197</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>Sub Total</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="V23" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5" t="inlineStr"/>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>T1:R4:C5</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>67.00</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="n">
         <v>182.358</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>154.15</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>191.495</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>177.994</v>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="n">
         <v>0.999986219406128</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>67.00</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr"/>
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="5" t="inlineStr"/>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>T1:R5:C2</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="D25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Tax 10%</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Tax 10%</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Tax 10%</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="n">
         <v>201.416</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="J25" s="5" t="n">
         <v>564.206</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="K25" s="5" t="n">
         <v>211.858</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="L25" s="5" t="n">
         <v>601.15</v>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="n">
         <v>0.9998850737299237</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>Tax 10%</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="5" t="inlineStr"/>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>T1:R5:C5</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="D26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>6.70</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="n">
         <v>201.938</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="J26" s="5" t="n">
         <v>154.412</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="K26" s="5" t="n">
         <v>212.119</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="L26" s="5" t="n">
         <v>173.278</v>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="n">
         <v>0.999992698431015</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="inlineStr">
         <is>
           <t>6.70</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="R26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="V26" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="5" t="inlineStr"/>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>T1:R6:C2</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="C27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="D27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="n">
         <v>221.256</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="J27" s="5" t="n">
         <v>551.891</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="K27" s="5" t="n">
         <v>232.482</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="L27" s="5" t="n">
         <v>600.888</v>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="n">
         <v>0.9999501434239474</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="V27" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
+          <t>T1:R6:C5</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
           <t>Data 1</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>73.70</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>73.70</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>73.70</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="n">
         <v>222.3</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="J28" s="5" t="n">
         <v>154.412</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>231.437</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>178.256</v>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>ocr-rapidocr</t>
         </is>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>ocr_score</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="n">
         <v>0.9999887943267822</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>Engine-reported recognition confidence; not measured accuracy.</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>73.70</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr">
         <is>
           <t>extracted</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>exact_source_box</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
         <is>
           <t>located</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="V28" s="5" t="inlineStr">
         <is>
           <t>At least one original reading has an exact source bounding box.</t>
         </is>
       </c>
+      <c r="W28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O28"/>
+  <autoFilter ref="A1:X28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3932,7 +5239,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>340786a4807cc812b4c6f75fc1f6dcbc6176daf566c2fb83ab046afbc3ee3046</t>
+          <t>960dc3da78458d4c0d20561c16bb66f07f35bb53ea2eecdf84bb428d4f26919e</t>
         </is>
       </c>
     </row>
